--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.1.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.1.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="60" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L258: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: St. John, Aug. 5.â€” A telegram</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]0</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]0</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: D</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]0</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -640,7 +644,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L215: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to relatives here announces the •</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr">
@@ -665,7 +673,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>822</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -684,12 +692,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L474: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5.â€”C. N. Armstrong,</t>
+          <t>L108: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -701,7 +709,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: M</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -715,7 +723,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L217: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • de Bellevue. He was the second •</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -747,12 +759,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: VOL. 23.â€”No. 182</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -764,7 +776,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L19: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -778,7 +790,11 @@
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L218: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+2666 BLACK DIAMOND SUIT | line starts with punctuation glued to text :: • son of the late Sir S. L. Tilley. ♦</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -794,12 +810,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -810,12 +826,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€‚.</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mexico City, Aug. 5.â€” How Matthew Gourd, an American</t>
+          <t>L214: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ St. John, Aug. 5.—A telegram •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -827,7 +843,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: P.</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -873,12 +889,12 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moncton, Aug. 5.â€”A. R. Mosher,</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Washington, Aug. 5.â€”That no an-</t>
+          <t>L215: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to relatives here announces the •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -890,7 +906,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: M.</t>
+          <t>L25: isolated marker/symbol line :: P.</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -936,24 +952,24 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L755: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Calgary, Alta., Aug. 5.â€”Fred Star-</t>
+          <t>L112: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mexico City, Aug. 5â€”The news of</t>
+          <t>L216: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ death of L. A. Tilley, at St. Anne °</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 8</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: L</t>
+          <t>L27: isolated marker/symbol line :: M.</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -999,24 +1015,24 @@
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Dexter McCluskeyâ€”Vice-President.</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+5143 CJK UNIFIED IDEOGRAPH-5143 | isolated marker/symbol line :: 元</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5.â€”The Times' Buch-</t>
+          <t>L217: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • de Bellevue. He was the second •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: P.</t>
+          <t>L108: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: L.</t>
+          <t>L31: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1062,24 +1078,24 @@
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L827: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. Jarvisâ€”Treasurer.</t>
+          <t>L473: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ St. John, Aug. 5.â€”A telegram â€¢</t>
+          <t>L218: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+2666 BLACK DIAMOND SUIT | line starts with punctuation glued to text :: • son of the late Sir S. L. Tilley. ♦</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: M.</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: -</t>
+          <t>L33: isolated marker/symbol line :: L.</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1105,12 +1121,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1121,24 +1137,24 @@
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L829: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Clark and P. Potterâ€”Committee.</t>
+          <t>L523: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L215: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ to relatives here announces the â€¢</t>
+          <t>L332: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 4</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L43: symbol-only separator/garbage line :: 1913.</t>
+          <t>L35: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1169,7 +1185,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1180,24 +1196,20 @@
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5 â€” The two British</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ death of L. A. Tilley, at St. Anne Â°</t>
-        </is>
-      </c>
+          <t>L524: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 2</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L211: symbol-only separator/garbage line :: ****************</t>
+          <t>L43: symbol-only separator/garbage line :: 1913.</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1219,12 +1231,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1235,24 +1247,20 @@
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ de Bellevue. He was the second â€¢</t>
-        </is>
-      </c>
+          <t>L595: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。.</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: .</t>
+          <t>L112: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L219: symbol-only separator/garbage line :: ****************</t>
+          <t>L211: symbol-only separator/garbage line :: ****************</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1288,22 +1296,22 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L218: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â€¢ son of the late Sir S. L. Tilley. â™¦</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L176: isolated marker/symbol line :: 1</t>
+          <t>L113: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L323: isolated marker/symbol line :: /</t>
+          <t>L219: symbol-only separator/garbage line :: ****************</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1330,7 +1338,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1340,21 +1348,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug 5.â€”The Washington</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L221: isolated marker/symbol line :: 2</t>
+          <t>L114: isolated marker/symbol line :: P.</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L332: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L323: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1391,21 +1395,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Admiraltyâ€™s plans relative to the</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L255: symbol-only separator/garbage line :: 367.00</t>
+          <t>L115: isolated marker/symbol line :: M.</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L373: isolated marker/symbol line :: 0</t>
+          <t>L332: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1442,21 +1442,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Britâ€™sh squadron in those waters and</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L257: symbol-only separator/garbage line :: 500.00</t>
+          <t>L116: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L374: isolated marker/symbol line :: J</t>
+          <t>L373: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1493,21 +1489,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Fisherâ€™s regime.</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L122: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: U</t>
+          <t>L374: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1532,21 +1524,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ceived in Bonusesâ€”Premier Flemming Pleased</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L525: isolated marker/symbol line :: b</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+5143 CJK UNIFIED IDEOGRAPH-5143 | isolated marker/symbol line :: 元</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L567: isolated marker/symbol line :: 0</t>
+          <t>L565: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1571,21 +1559,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”The Government Meeting.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L546: isolated marker/symbol line :: 55</t>
+          <t>L124: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L568: isolated marker/symbol line :: U.</t>
+          <t>L567: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1610,21 +1594,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L332: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L594: isolated marker/symbol line :: h</t>
+          <t>L176: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L572: isolated marker/symbol line :: 0</t>
+          <t>L568: isolated marker/symbol line :: U.</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1649,21 +1629,17 @@
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5â€”Premier Asquith</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L596: symbol-only separator/garbage line :: 75.00</t>
+          <t>L221: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L573: isolated marker/symbol line :: b</t>
+          <t>L572: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1688,21 +1664,17 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago, Ill., Aug. 5â€”Chicago's ten</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L598: symbol-only separator/garbage line :: 100.00</t>
+          <t>L255: symbol-only separator/garbage line :: 367.00</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L617: symbol-only separator/garbage line :: $967.50</t>
+          <t>L573: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1727,21 +1699,17 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L445: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5.â€”The lightning recently struck the</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L600: symbol-only separator/garbage line :: 50.00</t>
+          <t>L257: symbol-only separator/garbage line :: 500.00</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L618: symbol-only separator/garbage line :: 367.00</t>
+          <t>L617: symbol-only separator/garbage line :: $967.50</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1766,21 +1734,17 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L448: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: a part of if willâ€™ have to be taken</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L602: symbol-only separator/garbage line :: .$ 2, 059.50</t>
+          <t>L473: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L619: symbol-only separator/garbage line :: 500.00</t>
+          <t>L618: symbol-only separator/garbage line :: 367.00</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1805,21 +1769,17 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Gibson, N. B., Aug. 5.â€”The fire and</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L523: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L621: symbol-only separator/garbage line :: 75.00</t>
+          <t>L619: symbol-only separator/garbage line :: 500.00</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1844,21 +1804,17 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5.â€”Although the Mo-</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L849: isolated marker/symbol line :: .</t>
+          <t>L524: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L623: symbol-only separator/garbage line :: 100.00</t>
+          <t>L621: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1883,21 +1839,17 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L545: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Austin, Tex., Aug. 5.â€”It is planned</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L851: isolated marker/symbol line :: C</t>
+          <t>L525: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L625: symbol-only separator/garbage line :: 50.00</t>
+          <t>L623: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1922,17 +1874,17 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 5.â€”The Blue</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>L546: isolated marker/symbol line :: 55</t>
+        </is>
+      </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L651: isolated marker/symbol line :: 01</t>
+          <t>L625: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1957,17 +1909,17 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5.â€”C. N. Armstrong,</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>L594: isolated marker/symbol line :: h</t>
+        </is>
+      </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L751: isolated marker/symbol line :: =</t>
+          <t>L651: isolated marker/symbol line :: 01</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1992,17 +1944,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L658: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Toronto, Aug. 5â€”Rev. J. E. Sander-</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>L595: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。.</t>
+        </is>
+      </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L751: isolated marker/symbol line :: =</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2027,17 +1979,17 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: morning from St. Johnâ€™s, Newfound-</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>L596: symbol-only separator/garbage line :: 75.00</t>
+        </is>
+      </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L1046: isolated marker/symbol line :: -</t>
+          <t>L786: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2062,17 +2014,17 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L711: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Calgary, Alta., Aug. 5.â€”Fred Star-</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>L598: symbol-only separator/garbage line :: 100.00</t>
+        </is>
+      </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L1048: isolated marker/symbol line :: -</t>
+          <t>L1046: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2097,17 +2049,17 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Florence, Aug. F.â€”Jewelry to the</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>L600: symbol-only separator/garbage line :: 50.00</t>
+        </is>
+      </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L1050: isolated marker/symbol line :: %</t>
+          <t>L1048: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2132,15 +2084,19 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Toronto, Aug. 5.â€”While asleep in</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>L602: symbol-only separator/garbage line :: .$ 2, 059.50</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L1050: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2163,14 +2119,14 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L780: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5.â€”The Daily Express</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
+        </is>
+      </c>
       <c r="O35" s="1" t="inlineStr"/>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
@@ -2194,14 +2150,14 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>L849: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
       <c r="O36" s="1" t="inlineStr"/>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
@@ -2225,14 +2181,14 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Woodstock, N. B., Aug. 5.â€”Wilis</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>L851: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
       <c r="O37" s="1" t="inlineStr"/>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
@@ -2245,285 +2201,6 @@
       <c r="X37" s="1" t="inlineStr"/>
       <c r="Y37" s="1" t="inlineStr"/>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: T. G. Jonesâ€”President.</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A. W. Clarkâ€”Recording Secretary.</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L811: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Clark and P. Potterâ€”Committee.</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L930: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Berlin, Aug. 5.â€”The Tageliche</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Todayâ€™s Ball Games.</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L973: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moncton, Aug. 5.â€” A. R. Mosher,</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L988: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 5â€”The two British</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1006: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 New York, Aug. 5.â€”Patrick</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1039: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ing at 10 oâ€™clock.</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
